--- a/research/study_002_foundation_model_comparison/analysis/statistical_outputs/assumption_tests.xlsx
+++ b/research/study_002_foundation_model_comparison/analysis/statistical_outputs/assumption_tests.xlsx
@@ -1,15 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\3-6-2023\muawia 03-06-2026\Agentic-AI-research\research\study_002_foundation_model_comparison\analysis\statistical_outputs\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DF67657-5816-408A-BC37-ED38C0A39821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-23148" yWindow="1056" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Overview" sheetId="1" r:id="rId1"/>
+    <sheet name="Normality_Quality" sheetId="2" r:id="rId2"/>
+    <sheet name="Normality_Confidence" sheetId="3" r:id="rId3"/>
+    <sheet name="Homogeneity_Quality" sheetId="4" r:id="rId4"/>
+    <sheet name="Homogeneity_Confidence" sheetId="5" r:id="rId5"/>
+    <sheet name="Formal_Tests" sheetId="8" r:id="rId6"/>
+    <sheet name="Decision" sheetId="6" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -18,11 +30,260 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="76">
+  <si>
+    <t>Summary of statistical assumption testing for Study 002.</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Study002 AnalysisReady</t>
+  </si>
+  <si>
+    <t>Total Observations</t>
+  </si>
+  <si>
+    <t>Providers</t>
+  </si>
+  <si>
+    <t>Workflows</t>
+  </si>
+  <si>
+    <t>Primary Outcome</t>
+  </si>
+  <si>
+    <t>quality_score</t>
+  </si>
+  <si>
+    <t>Secondary Outcome</t>
+  </si>
+  <si>
+    <t>confidence</t>
+  </si>
+  <si>
+    <t>Planned Analysis</t>
+  </si>
+  <si>
+    <t>Two-Way ANOVA</t>
+  </si>
+  <si>
+    <t>Assumption Checks</t>
+  </si>
+  <si>
+    <t>Normality, Homogeneity</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Provider</t>
+  </si>
+  <si>
+    <t>Workflow</t>
+  </si>
+  <si>
+    <t>OpenAI</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Mean</t>
+  </si>
+  <si>
+    <t>Median</t>
+  </si>
+  <si>
+    <t>SD</t>
+  </si>
+  <si>
+    <t>Anthropic</t>
+  </si>
+  <si>
+    <t>basic_agent</t>
+  </si>
+  <si>
+    <t>planner_executor</t>
+  </si>
+  <si>
+    <t>planner_executor_reviewer</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>Variance Equality</t>
+  </si>
+  <si>
+    <t>Grouping Factor</t>
+  </si>
+  <si>
+    <t>Max Variance</t>
+  </si>
+  <si>
+    <t>Min Variance</t>
+  </si>
+  <si>
+    <t>Variance Ratio</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Assumption</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Quality Normality</t>
+  </si>
+  <si>
+    <t>Confidence Normality</t>
+  </si>
+  <si>
+    <t>Quality Homogeneity</t>
+  </si>
+  <si>
+    <t>Confidence Homogeneity</t>
+  </si>
+  <si>
+    <t>Approx. Normal</t>
+  </si>
+  <si>
+    <t>Mild Skew</t>
+  </si>
+  <si>
+    <t>Ceiling Effect</t>
+  </si>
+  <si>
+    <t>Potential Non-Normal</t>
+  </si>
+  <si>
+    <t>Strong Ceiling Effect</t>
+  </si>
+  <si>
+    <t>Assessment of confidence score distributions across provider × workflow groups using descriptive indicators (mean, median, and standard deviation). Formal normality tests will be conducted separately where applicable.</t>
+  </si>
+  <si>
+    <t>Assessment Criteria:</t>
+  </si>
+  <si>
+    <t>- Ceiling Effect: Values cluster near the upper bound (1.0), reducing variability.</t>
+  </si>
+  <si>
+    <t>- Strong Ceiling Effect: Values are highly concentrated near 1.0 with very low variability.</t>
+  </si>
+  <si>
+    <t>- Approx. Normal: Mean and median are closely aligned with no evidence of strong boundary effects.</t>
+  </si>
+  <si>
+    <t>- Mild Skew: Moderate difference between mean and median suggests mild distributional asymmetry.</t>
+  </si>
+  <si>
+    <t>"Initial distributional assessment based on mean-median agreement and variability patterns suggested generally acceptable distributional behavior, with ceiling effects observed in selected Google workflow groups."</t>
+  </si>
+  <si>
+    <t>Assessment of quality score distributions across provider × workflow groups using descriptive indicators (mean, median, and standard deviation). Formal normality tests will be conducted separately where applicable.</t>
+  </si>
+  <si>
+    <t>- Potential Non-Normal: Large mean–median discrepancy and high variability suggest possible deviation from normality.</t>
+  </si>
+  <si>
+    <t>Heterogeneity Observed</t>
+  </si>
+  <si>
+    <t>Balanced Experimental Design</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Cell Size per Group</t>
+  </si>
+  <si>
+    <t>Final Decision</t>
+  </si>
+  <si>
+    <t>Rejected (Shapiro-Wilk)</t>
+  </si>
+  <si>
+    <t>Rejected in 8 of 9 groups (Shapiro-Wilk)</t>
+  </si>
+  <si>
+    <t>Rejected (Levene's Test)</t>
+  </si>
+  <si>
+    <t>Formal assumption testing indicated significant departures from normality and homogeneity of variance. However, the experimental design is fully balanced (3 × 3 factorial design with n = 30 observations per provider × workflow group). Given the robustness of factorial ANOVA to moderate assumption violations under balanced designs, Two-Way ANOVA was retained as the primary inferential analysis method. Results should be interpreted alongside effect size estimates and post-hoc analyses.</t>
+  </si>
+  <si>
+    <t>Shapiro-Wilk Summary</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Groups Tested</t>
+  </si>
+  <si>
+    <t>Normality Rejected</t>
+  </si>
+  <si>
+    <t>Normality Not Rejected</t>
+  </si>
+  <si>
+    <t>Levene Summary</t>
+  </si>
+  <si>
+    <t>Statistic</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>Equal variances rejected</t>
+  </si>
+  <si>
+    <t>Completed - Descriptive and Formal Assumption Testing</t>
+  </si>
+  <si>
+    <t>Most confidence score distributions appear approximately normal. However, Google planner_executor and planner_executor_reviewer exhibit ceiling effects due to confidence values clustering near the upper bound of 1.0. These deviations are not unexpected given the bounded nature of confidence scores. The balanced experimental design (n = 30 per provider × workflow group) supports the continued use of parametric methods</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,13 +310,153 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="43">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +467,114 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4752D896-A41A-4FB7-95D1-9622EA79F339}" name="Table1" displayName="Table1" ref="A4:B13" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
+  <autoFilter ref="A4:B13" xr:uid="{4752D896-A41A-4FB7-95D1-9622EA79F339}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{6BA30200-FBAE-4A7D-ACA7-5A95BF177EDE}" name="Item" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{2FC11A41-7258-42C4-8682-803C867ABA13}" name="Value" dataDxfId="41"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{30E64E18-F179-48CC-BC8A-BBE93C7B3793}" name="Table10" displayName="Table10" ref="A5:G14" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+  <autoFilter ref="A5:G14" xr:uid="{30E64E18-F179-48CC-BC8A-BBE93C7B3793}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{A34901A8-9034-4895-AB37-A43F99F6457A}" name="Provider" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{853CE438-7015-49E9-8809-4C9C4AAF29D1}" name="Workflow" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{28EE18E7-7CC3-40E0-8D18-4B61264EFE68}" name="N" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{C2804A39-B1E6-471D-9F58-5CAD38ABB2E9}" name="Mean" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{C41E660D-2796-4DF8-A239-A267BBB9EF62}" name="Median" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{29C321EA-6523-43E5-942F-BDF68AB42453}" name="SD" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{D116CEBA-8155-427E-AB5B-C396A2C9C25F}" name="Assessment" dataDxfId="32"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D23DA841-540B-4427-A103-079C3B59948B}" name="Table9" displayName="Table9" ref="A5:G14" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+  <autoFilter ref="A5:G14" xr:uid="{D23DA841-540B-4427-A103-079C3B59948B}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{F64193CC-34A2-4B8C-9570-795955621D4E}" name="Provider" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{DF29DE8C-F9D8-4CE2-8917-6DF488C81E09}" name="Workflow" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{DE477EC0-E881-4D6F-8A5F-98B3971233D0}" name="N" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{5C210485-C765-4753-8B1A-09BF6B505A0C}" name="Mean" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{2BE09FF2-BA4B-47A3-A950-2EB729D569C1}" name="Median" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{706274AE-A17C-483E-8536-BE615D8E03DA}" name="SD" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{056F9A1A-7492-4130-82FA-872E9E188FF1}" name="Assessment" dataDxfId="25"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{E47AC761-F565-4640-B8D7-FE48ADB06578}" name="Table4" displayName="Table4" ref="A4:E6" totalsRowShown="0" headerRowDxfId="14" dataDxfId="15">
+  <autoFilter ref="A4:E6" xr:uid="{E47AC761-F565-4640-B8D7-FE48ADB06578}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A6EC45FA-3EAE-4642-8DCF-58FE1712E349}" name="Grouping Factor" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{0FE4014F-BEB1-4215-8727-EBB6AAE13611}" name="Max Variance" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{7F699D36-62EB-4E28-B5A5-DAB9021D80E0}" name="Min Variance" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{8D24DB96-6AC5-4F2F-BA1B-26D449E4D6CD}" name="Variance Ratio" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{16E833C8-0B0E-4B1A-89F6-E78D5C85D37C}" name="Assessment" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{583A0314-CE5C-4DCE-9887-40FBCC0D3A17}" name="Table46" displayName="Table46" ref="A4:E6" totalsRowShown="0">
+  <autoFilter ref="A4:E6" xr:uid="{583A0314-CE5C-4DCE-9887-40FBCC0D3A17}"/>
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{A3027F58-5ABC-47C4-A200-F1DEB1FBA3AE}" name="Grouping Factor"/>
+    <tableColumn id="2" xr3:uid="{6D5EF6E5-2422-42C9-8D63-908FB5A71365}" name="Max Variance" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B42BD7FD-A673-4607-9317-D9080D5792E9}" name="Min Variance" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{13AB4711-7A0F-4C2A-A855-9B362EB85E74}" name="Variance Ratio" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{9FFA4E8F-6A66-4004-84C9-72276FA77B48}" name="Assessment" dataDxfId="10"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{95AFA56D-1900-41B7-B6C4-C238776940D0}" name="Table14" displayName="Table14" ref="A3:D5" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A3:D5" xr:uid="{95AFA56D-1900-41B7-B6C4-C238776940D0}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{348679C4-EF7B-4438-B8A6-3728C55F9D87}" name="Outcome" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4477F929-B3E6-483B-8F59-6B34308E980F}" name="Groups Tested" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{544C85C2-C902-4D9C-96EA-B1FD6DF29C29}" name="Normality Rejected" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{BD4D8B72-8DCB-4931-A33A-E955DF372F61}" name="Normality Not Rejected" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{056AC69C-4A36-4799-B0B6-7EA8C41358E2}" name="Table15" displayName="Table15" ref="A11:D13" totalsRowShown="0">
+  <autoFilter ref="A11:D13" xr:uid="{056AC69C-4A36-4799-B0B6-7EA8C41358E2}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{CAF05889-CD2F-4C8B-9957-0C6108F7FDE9}" name="Outcome"/>
+    <tableColumn id="2" xr3:uid="{AD9B3BA9-B144-4C6E-8077-CE4F975A0C95}" name="Statistic"/>
+    <tableColumn id="3" xr3:uid="{BE99FF05-F511-4173-B259-6286E06A88EC}" name="p-value"/>
+    <tableColumn id="4" xr3:uid="{A42CD8BE-80C4-4B09-8870-6A1584BF643C}" name="Result"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{A55A6DDE-35A5-4B95-A978-724C349A38DD}" name="Table6" displayName="Table6" ref="A2:B8" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
+  <autoFilter ref="A2:B8" xr:uid="{A55A6DDE-35A5-4B95-A978-724C349A38DD}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{1A37F949-FBE3-40AB-AED4-399A0EBD1C3A}" name="Assumption" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{DDBA9F2B-924C-459B-8EAF-FB84AC1F27F3}" name="Result" dataDxfId="6"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +839,1060 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.109375" customWidth="1"/>
+    <col min="2" max="2" width="47.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF3489E9-2C94-4C4A-921A-7DAF451DBD56}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="7" max="7" width="19.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.874</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.84099999999999997</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.88</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.246</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.314</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>30</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.89500000000000002</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="F14" s="1">
+        <v>3.1E-2</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE61AE34-B7A8-4BE0-B70D-0EF644980238}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="7" max="7" width="21" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="1">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.874</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="F6" s="1">
+        <v>0.17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0.92</v>
+      </c>
+      <c r="F7" s="1">
+        <v>0.10199999999999999</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0.88400000000000001</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="F8" s="1">
+        <v>6.0999999999999999E-2</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="1">
+        <v>30</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0.246</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="1">
+        <v>30</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="E10" s="1">
+        <v>1</v>
+      </c>
+      <c r="F10" s="1">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1">
+        <v>30</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0.996</v>
+      </c>
+      <c r="E11" s="1">
+        <v>1</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1.2999999999999999E-2</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1">
+        <v>30</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.03</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="1">
+        <v>30</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.93899999999999995</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0.95</v>
+      </c>
+      <c r="F13" s="1">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1">
+        <v>30</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0.94599999999999995</v>
+      </c>
+      <c r="E14" s="1">
+        <v>0.94499999999999995</v>
+      </c>
+      <c r="F14" s="1">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14ECADC8-AE70-4577-980C-6F9A32CAA001}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.21875" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1">
+        <v>9.8704022988505932E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>4.7126436781593292E-4</v>
+      </c>
+      <c r="D5" s="1">
+        <v>209.44512195129059</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1">
+        <v>9.8704022988505932E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>4.7126436781593292E-4</v>
+      </c>
+      <c r="D6" s="1">
+        <v>209.44512195129059</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96BEF23E-DAE3-40BF-86E1-C8C1D9CAF1E5}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1">
+        <v>6.073057471264369E-2</v>
+      </c>
+      <c r="C5" s="1">
+        <v>1.6965517241386327E-4</v>
+      </c>
+      <c r="D5" s="1">
+        <v>357.96476964754851</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="1">
+        <v>6.073057471264369E-2</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1.6965517241386327E-4</v>
+      </c>
+      <c r="D6" s="1">
+        <v>357.96476964754851</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E73B98DF-1867-42F2-BC86-ECC17D3D55C7}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>5.5350000000000001</v>
+      </c>
+      <c r="C12">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>2.0609999999999999</v>
+      </c>
+      <c r="C13">
+        <v>4.0025999999999999E-2</v>
+      </c>
+      <c r="D13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9357B0D3-1E08-4D9D-A975-E89F515C22D5}">
+  <dimension ref="A2:B14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>